--- a/dados/SURVEY_VESSELS/SURVEY_VESSELS_20260801_manha.xlsx
+++ b/dados/SURVEY_VESSELS/SURVEY_VESSELS_20260801_manha.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cefetrjbr-my.sharepoint.com/personal/12396387790_cefet-rj_br/Documents/Empresas e entrevistas/projeto logistica offshore/ofi/dados/SURVEY_VESSELS/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="957" documentId="8_{2FDA8D28-226B-473E-B58F-AB3C8EEAFC38}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5DDCB24B-52E1-4F19-8216-8734A600792A}"/>
+  <xr:revisionPtr revIDLastSave="1028" documentId="8_{2FDA8D28-226B-473E-B58F-AB3C8EEAFC38}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7D6743E2-2F5F-4CAA-8B6B-32ADD4812534}"/>
   <bookViews>
-    <workbookView xWindow="-96" yWindow="0" windowWidth="11712" windowHeight="12336" activeTab="3" xr2:uid="{FAEFD476-B005-4995-A964-6D919B2AA8E5}"/>
+    <workbookView xWindow="-105" yWindow="0" windowWidth="14610" windowHeight="15585" activeTab="1" xr2:uid="{FAEFD476-B005-4995-A964-6D919B2AA8E5}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="153" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="230" uniqueCount="101">
   <si>
     <t>cbo</t>
   </si>
@@ -237,6 +237,114 @@
   </si>
   <si>
     <t>status</t>
+  </si>
+  <si>
+    <t>At Anchor</t>
+  </si>
+  <si>
+    <t>Underway using Engine</t>
+  </si>
+  <si>
+    <t>Stopped</t>
+  </si>
+  <si>
+    <t>Moored</t>
+  </si>
+  <si>
+    <t>Restricted Manoeuvrability</t>
+  </si>
+  <si>
+    <t>BRAM ATLAS</t>
+  </si>
+  <si>
+    <t>BRAM BAHIA</t>
+  </si>
+  <si>
+    <t>BRAM BELEM</t>
+  </si>
+  <si>
+    <t>BRAM BRASIL</t>
+  </si>
+  <si>
+    <t>BRAM BRASILIA</t>
+  </si>
+  <si>
+    <t>BRAM BRAVO</t>
+  </si>
+  <si>
+    <t>BRAM BREEZE</t>
+  </si>
+  <si>
+    <t>BRAM BUCK</t>
+  </si>
+  <si>
+    <t>BRAM BUZIOS</t>
+  </si>
+  <si>
+    <t>BRAM HERO</t>
+  </si>
+  <si>
+    <t>CBO ALESSANDRA</t>
+  </si>
+  <si>
+    <t>CBO ALIANCA</t>
+  </si>
+  <si>
+    <t>CBO ANITA</t>
+  </si>
+  <si>
+    <t>CBO ARPOADOR</t>
+  </si>
+  <si>
+    <t>CBO CAMPOS</t>
+  </si>
+  <si>
+    <t>CBO CAROLINA</t>
+  </si>
+  <si>
+    <t>CBO COPACABANA</t>
+  </si>
+  <si>
+    <t>CBO ENERGY</t>
+  </si>
+  <si>
+    <t>CBO FLAMENGO</t>
+  </si>
+  <si>
+    <t>CBO IPANEMA</t>
+  </si>
+  <si>
+    <t>CBO ISABELLA</t>
+  </si>
+  <si>
+    <t>CBO ITAJAI</t>
+  </si>
+  <si>
+    <t>CBO MANOELLA</t>
+  </si>
+  <si>
+    <t>CBO OCEANA</t>
+  </si>
+  <si>
+    <t>CBO RENATA</t>
+  </si>
+  <si>
+    <t>CBO RIO</t>
+  </si>
+  <si>
+    <t>Class B</t>
+  </si>
+  <si>
+    <t>CBO SUPPORTER</t>
+  </si>
+  <si>
+    <t>CBO VITORIA</t>
+  </si>
+  <si>
+    <t>CBO WAVE</t>
+  </si>
+  <si>
+    <t>CBO WISER</t>
   </si>
 </sst>
 </file>
@@ -639,15 +747,15 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{490C43E3-ED93-4C78-B9B5-276EDD51C5AB}">
   <dimension ref="A1:D23"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="16.44140625" customWidth="1"/>
-    <col min="2" max="2" width="13.6640625" customWidth="1"/>
+    <col min="1" max="1" width="16.42578125" customWidth="1"/>
+    <col min="2" max="2" width="13.7109375" customWidth="1"/>
     <col min="3" max="3" width="17" customWidth="1"/>
-    <col min="4" max="4" width="26.77734375" customWidth="1"/>
+    <col min="4" max="4" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -661,7 +769,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>39</v>
       </c>
@@ -675,7 +783,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>45</v>
       </c>
@@ -689,7 +797,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>9</v>
       </c>
@@ -703,7 +811,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>6</v>
       </c>
@@ -717,7 +825,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>51</v>
       </c>
@@ -731,7 +839,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>57</v>
       </c>
@@ -745,7 +853,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>38</v>
       </c>
@@ -759,7 +867,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>47</v>
       </c>
@@ -773,7 +881,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>4</v>
       </c>
@@ -787,7 +895,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>5</v>
       </c>
@@ -801,7 +909,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>11</v>
       </c>
@@ -815,7 +923,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>46</v>
       </c>
@@ -829,7 +937,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>10</v>
       </c>
@@ -843,7 +951,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>44</v>
       </c>
@@ -857,7 +965,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>7</v>
       </c>
@@ -868,7 +976,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>50</v>
       </c>
@@ -879,7 +987,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>37</v>
       </c>
@@ -890,7 +998,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>49</v>
       </c>
@@ -898,7 +1006,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>36</v>
       </c>
@@ -906,17 +1014,17 @@
         <v>35</v>
       </c>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>8</v>
       </c>
@@ -929,19 +1037,20 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{93DC0AFA-9444-4F11-ABC1-7475EEC3A448}">
   <dimension ref="A1:O27"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="2" width="16.44140625" customWidth="1"/>
-    <col min="3" max="3" width="15.109375" customWidth="1"/>
-    <col min="6" max="6" width="20.77734375" customWidth="1"/>
-    <col min="7" max="7" width="12.44140625" customWidth="1"/>
-    <col min="8" max="8" width="23.21875" customWidth="1"/>
+    <col min="1" max="1" width="16.42578125" customWidth="1"/>
+    <col min="2" max="2" width="21.5703125" customWidth="1"/>
+    <col min="3" max="3" width="15.140625" customWidth="1"/>
+    <col min="6" max="6" width="20.7109375" customWidth="1"/>
+    <col min="7" max="7" width="12.42578125" customWidth="1"/>
+    <col min="8" max="8" width="23.28515625" customWidth="1"/>
     <col min="11" max="11" width="21" customWidth="1"/>
-    <col min="13" max="13" width="14.109375" customWidth="1"/>
-    <col min="14" max="14" width="14.44140625" customWidth="1"/>
+    <col min="13" max="13" width="14.140625" customWidth="1"/>
+    <col min="14" max="14" width="14.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -967,247 +1076,507 @@
         <v>64</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>39</v>
       </c>
-      <c r="B2" s="6"/>
-      <c r="C2" s="1"/>
-      <c r="D2" s="1"/>
-      <c r="E2" s="1"/>
-      <c r="F2" s="6"/>
+      <c r="B2" s="6">
+        <v>46235.407638888886</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="D2" s="1">
+        <v>-22.843443000000001</v>
+      </c>
+      <c r="E2" s="1">
+        <v>-43.129742</v>
+      </c>
+      <c r="F2" s="6">
+        <v>46235.405555555553</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>65</v>
+      </c>
       <c r="H2" s="1"/>
       <c r="I2" s="1"/>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>45</v>
       </c>
-      <c r="B3" s="6"/>
-      <c r="C3" s="1"/>
-      <c r="D3" s="1"/>
-      <c r="E3" s="1"/>
-      <c r="F3" s="6"/>
+      <c r="B3" s="6">
+        <v>46235.407638888886</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="D3" s="1">
+        <v>-25.617207000000001</v>
+      </c>
+      <c r="E3" s="1">
+        <v>-42.841625000000001</v>
+      </c>
+      <c r="F3" s="6">
+        <v>46232.576388888891</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>67</v>
+      </c>
       <c r="H3" s="1"/>
       <c r="I3" s="1"/>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>9</v>
       </c>
-      <c r="B4" s="6"/>
-      <c r="C4" s="1"/>
-      <c r="D4" s="1"/>
-      <c r="E4" s="1"/>
-      <c r="F4" s="6"/>
+      <c r="B4" s="6">
+        <v>46235.407638888886</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="D4" s="1">
+        <v>-23.513812999999999</v>
+      </c>
+      <c r="E4" s="1">
+        <v>-41.065894999999998</v>
+      </c>
+      <c r="F4" s="6">
+        <v>46235.086805555555</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>67</v>
+      </c>
       <c r="H4" s="1"/>
       <c r="I4" s="1"/>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>6</v>
       </c>
-      <c r="B5" s="6"/>
-      <c r="C5" s="1"/>
-      <c r="D5" s="1"/>
-      <c r="E5" s="1"/>
-      <c r="F5" s="6"/>
+      <c r="B5" s="6">
+        <v>46235.407638888886</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="D5" s="1">
+        <v>-22.881622</v>
+      </c>
+      <c r="E5" s="1">
+        <v>-43.117462000000003</v>
+      </c>
+      <c r="F5" s="6">
+        <v>46235.404861111114</v>
+      </c>
+      <c r="G5" s="1" t="s">
+        <v>68</v>
+      </c>
       <c r="H5" s="1"/>
       <c r="I5" s="1"/>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>51</v>
       </c>
-      <c r="B6" s="6"/>
-      <c r="C6" s="1"/>
-      <c r="D6" s="1"/>
-      <c r="E6" s="1"/>
-      <c r="F6" s="6"/>
+      <c r="B6" s="6">
+        <v>46235.407638888886</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="D6" s="1">
+        <v>-22.864473</v>
+      </c>
+      <c r="E6" s="1">
+        <v>-43.109585000000003</v>
+      </c>
+      <c r="F6" s="6">
+        <v>44390.56527777778</v>
+      </c>
+      <c r="G6" s="1" t="s">
+        <v>68</v>
+      </c>
       <c r="H6" s="1"/>
       <c r="I6" s="1"/>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>38</v>
       </c>
-      <c r="B7" s="6"/>
-      <c r="C7" s="1"/>
-      <c r="D7" s="1"/>
-      <c r="E7" s="1"/>
-      <c r="F7" s="6"/>
+      <c r="B7" s="6">
+        <v>46235.407638888886</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="D7" s="1">
+        <v>-23.421261000000001</v>
+      </c>
+      <c r="E7" s="1">
+        <v>-42.944679000000001</v>
+      </c>
+      <c r="F7" s="6">
+        <v>46235.394444444442</v>
+      </c>
+      <c r="G7" s="1" t="s">
+        <v>66</v>
+      </c>
       <c r="H7" s="1"/>
       <c r="I7" s="1"/>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>57</v>
       </c>
-      <c r="B8" s="6"/>
-      <c r="C8" s="1"/>
-      <c r="D8" s="1"/>
-      <c r="E8" s="1"/>
-      <c r="F8" s="6"/>
+      <c r="B8" s="6">
+        <v>46235.407638888886</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="D8" s="1">
+        <v>-22.894600000000001</v>
+      </c>
+      <c r="E8" s="1">
+        <v>-43.212166000000003</v>
+      </c>
+      <c r="F8" s="6">
+        <v>46235.404861111114</v>
+      </c>
+      <c r="G8" s="1" t="s">
+        <v>68</v>
+      </c>
       <c r="H8" s="1"/>
       <c r="I8" s="1"/>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>47</v>
       </c>
-      <c r="B9" s="6"/>
-      <c r="C9" s="1"/>
-      <c r="D9" s="1"/>
-      <c r="E9" s="1"/>
-      <c r="F9" s="6"/>
+      <c r="B9" s="6">
+        <v>46235.407638888886</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="D9" s="1">
+        <v>-23.313922999999999</v>
+      </c>
+      <c r="E9" s="1">
+        <v>-43.128742000000003</v>
+      </c>
+      <c r="F9" s="6">
+        <v>46235.061111111114</v>
+      </c>
+      <c r="G9" s="1" t="s">
+        <v>66</v>
+      </c>
       <c r="H9" s="1"/>
       <c r="I9" s="1"/>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>4</v>
       </c>
-      <c r="B10" s="6"/>
-      <c r="C10" s="1"/>
-      <c r="D10" s="1"/>
-      <c r="E10" s="1"/>
-      <c r="F10" s="6"/>
+      <c r="B10" s="6">
+        <v>46235.407638888886</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="D10" s="1">
+        <v>-21.978467999999999</v>
+      </c>
+      <c r="E10" s="1">
+        <v>-39.766022</v>
+      </c>
+      <c r="F10" s="6">
+        <v>46235.177083333336</v>
+      </c>
+      <c r="G10" s="1" t="s">
+        <v>69</v>
+      </c>
       <c r="H10" s="1"/>
       <c r="I10" s="1"/>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>5</v>
       </c>
-      <c r="B11" s="6"/>
-      <c r="C11" s="1"/>
-      <c r="D11" s="1"/>
-      <c r="E11" s="1"/>
-      <c r="F11" s="6"/>
+      <c r="B11" s="6">
+        <v>46235.407638888886</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="D11" s="1">
+        <v>-23.563127999999999</v>
+      </c>
+      <c r="E11" s="1">
+        <v>-41.130524000000001</v>
+      </c>
+      <c r="F11" s="6">
+        <v>46235.114583333336</v>
+      </c>
+      <c r="G11" s="1" t="s">
+        <v>67</v>
+      </c>
       <c r="H11" s="1"/>
       <c r="I11" s="1"/>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>11</v>
       </c>
-      <c r="B12" s="6"/>
-      <c r="C12" s="1"/>
-      <c r="D12" s="1"/>
-      <c r="E12" s="1"/>
-      <c r="F12" s="6"/>
+      <c r="B12" s="6">
+        <v>46235.418055555558</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="D12" s="1">
+        <v>-22.894380999999999</v>
+      </c>
+      <c r="E12" s="1">
+        <v>-43.201912</v>
+      </c>
+      <c r="F12" s="6">
+        <v>46235.413194444445</v>
+      </c>
+      <c r="G12" s="1" t="s">
+        <v>68</v>
+      </c>
       <c r="H12" s="1"/>
       <c r="I12" s="1"/>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>46</v>
       </c>
-      <c r="B13" s="6"/>
-      <c r="C13" s="1"/>
-      <c r="D13" s="1"/>
-      <c r="E13" s="1"/>
-      <c r="F13" s="6"/>
+      <c r="B13" s="6">
+        <v>46235.418055555558</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="D13" s="1">
+        <v>-22.836293999999999</v>
+      </c>
+      <c r="E13" s="1">
+        <v>-43.128825999999997</v>
+      </c>
+      <c r="F13" s="6">
+        <v>46235.416666666664</v>
+      </c>
+      <c r="G13" s="1" t="s">
+        <v>65</v>
+      </c>
       <c r="H13" s="1"/>
       <c r="I13" s="1"/>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>10</v>
       </c>
-      <c r="B14" s="6"/>
-      <c r="C14" s="1"/>
-      <c r="D14" s="1"/>
-      <c r="E14" s="1"/>
-      <c r="F14" s="6"/>
+      <c r="B14" s="6">
+        <v>46235.418055555558</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="D14" s="1">
+        <v>-25.20393</v>
+      </c>
+      <c r="E14" s="1">
+        <v>-42.877555999999998</v>
+      </c>
+      <c r="F14" s="6">
+        <v>46232.605555555558</v>
+      </c>
+      <c r="G14" s="1" t="s">
+        <v>69</v>
+      </c>
       <c r="H14" s="1"/>
       <c r="I14" s="1"/>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>44</v>
       </c>
-      <c r="B15" s="6"/>
-      <c r="C15" s="1"/>
-      <c r="D15" s="1"/>
-      <c r="E15" s="1"/>
-      <c r="F15" s="6"/>
+      <c r="B15" s="6">
+        <v>46235.418055555558</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="D15" s="1">
+        <v>-22.895192999999999</v>
+      </c>
+      <c r="E15" s="1">
+        <v>-43.203777000000002</v>
+      </c>
+      <c r="F15" s="6">
+        <v>46235.416666666664</v>
+      </c>
+      <c r="G15" s="1" t="s">
+        <v>65</v>
+      </c>
       <c r="H15" s="1"/>
       <c r="I15" s="1"/>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>7</v>
       </c>
-      <c r="B16" s="6"/>
-      <c r="C16" s="1"/>
-      <c r="D16" s="1"/>
-      <c r="E16" s="1"/>
-      <c r="F16" s="6"/>
+      <c r="B16" s="6">
+        <v>46235.418055555558</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="D16" s="1">
+        <v>-21.214157</v>
+      </c>
+      <c r="E16" s="1">
+        <v>-39.998187999999999</v>
+      </c>
+      <c r="F16" s="6">
+        <v>46234.745138888888</v>
+      </c>
+      <c r="G16" s="1" t="s">
+        <v>67</v>
+      </c>
       <c r="H16" s="1"/>
       <c r="I16" s="1"/>
     </row>
-    <row r="17" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>50</v>
       </c>
-      <c r="B17" s="6"/>
-      <c r="C17" s="1"/>
-      <c r="D17" s="1"/>
-      <c r="E17" s="1"/>
-      <c r="F17" s="6"/>
+      <c r="B17" s="6">
+        <v>46235.418055555558</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="D17" s="1">
+        <v>-30.372271999999999</v>
+      </c>
+      <c r="E17" s="1">
+        <v>-47.695132999999998</v>
+      </c>
+      <c r="F17" s="6">
+        <v>44677.811111111114</v>
+      </c>
+      <c r="G17" s="1" t="s">
+        <v>96</v>
+      </c>
       <c r="H17" s="1"/>
       <c r="I17" s="1"/>
     </row>
-    <row r="18" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>37</v>
       </c>
-      <c r="B18" s="6"/>
-      <c r="C18" s="1"/>
-      <c r="D18" s="1"/>
-      <c r="E18" s="1"/>
-      <c r="F18" s="6"/>
+      <c r="B18" s="6">
+        <v>46235.418055555558</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="D18" s="1">
+        <v>-23.395835999999999</v>
+      </c>
+      <c r="E18" s="1">
+        <v>-41.408047000000003</v>
+      </c>
+      <c r="F18" s="6">
+        <v>46235.179861111108</v>
+      </c>
+      <c r="G18" s="1" t="s">
+        <v>66</v>
+      </c>
       <c r="H18" s="1"/>
       <c r="I18" s="1"/>
     </row>
-    <row r="19" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>49</v>
       </c>
-      <c r="B19" s="6"/>
-      <c r="C19" s="1"/>
-      <c r="D19" s="1"/>
-      <c r="E19" s="1"/>
-      <c r="F19" s="6"/>
+      <c r="B19" s="6">
+        <v>46235.418055555558</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="D19" s="1">
+        <v>-22.864526999999999</v>
+      </c>
+      <c r="E19" s="1">
+        <v>-43.111075999999997</v>
+      </c>
+      <c r="F19" s="6">
+        <v>45839.576388888891</v>
+      </c>
+      <c r="G19" s="1" t="s">
+        <v>68</v>
+      </c>
       <c r="H19" s="1"/>
       <c r="I19" s="1"/>
     </row>
-    <row r="20" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>36</v>
       </c>
-      <c r="B20" s="6"/>
-      <c r="C20" s="1"/>
-      <c r="D20" s="1"/>
-      <c r="E20" s="1"/>
-      <c r="F20" s="6"/>
+      <c r="B20" s="6">
+        <v>46235.418055555558</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="D20" s="1">
+        <v>-24.652591999999999</v>
+      </c>
+      <c r="E20" s="1">
+        <v>-42.235106999999999</v>
+      </c>
+      <c r="F20" s="6">
+        <v>46232.638888888891</v>
+      </c>
+      <c r="G20" s="1" t="s">
+        <v>69</v>
+      </c>
       <c r="H20" s="1"/>
       <c r="I20" s="1"/>
     </row>
-    <row r="21" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>48</v>
       </c>
-      <c r="B21" s="6"/>
-      <c r="C21" s="1"/>
-      <c r="D21" s="1"/>
-      <c r="E21" s="1"/>
-      <c r="F21" s="6"/>
+      <c r="B21" s="6">
+        <v>46235.418055555558</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="D21" s="1">
+        <v>-25.491667</v>
+      </c>
+      <c r="E21" s="1">
+        <v>-43.993332000000002</v>
+      </c>
+      <c r="F21" s="6">
+        <v>46233.682638888888</v>
+      </c>
+      <c r="G21" s="1" t="s">
+        <v>66</v>
+      </c>
       <c r="H21" s="1"/>
       <c r="I21" s="1"/>
     </row>
-    <row r="22" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>12</v>
       </c>
@@ -1220,7 +1589,7 @@
       <c r="J22" s="1"/>
       <c r="O22" s="4"/>
     </row>
-    <row r="23" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>8</v>
       </c>
@@ -1232,10 +1601,10 @@
       <c r="H23" s="1"/>
       <c r="J23" s="1"/>
     </row>
-    <row r="24" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:15" x14ac:dyDescent="0.25">
       <c r="J24" s="1"/>
     </row>
-    <row r="25" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:15" x14ac:dyDescent="0.25">
       <c r="D25" s="1"/>
       <c r="E25" s="1"/>
       <c r="F25" s="1"/>
@@ -1244,7 +1613,7 @@
       <c r="I25" s="1"/>
       <c r="J25" s="1"/>
     </row>
-    <row r="26" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:15" x14ac:dyDescent="0.25">
       <c r="D26" s="1"/>
       <c r="E26" s="1"/>
       <c r="F26" s="1"/>
@@ -1253,7 +1622,7 @@
       <c r="I26" s="1"/>
       <c r="J26" s="1"/>
     </row>
-    <row r="27" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:15" x14ac:dyDescent="0.25">
       <c r="J27" s="1"/>
     </row>
   </sheetData>
@@ -1267,20 +1636,23 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00B80E83-9236-40C9-95ED-72F039A44EB0}">
   <dimension ref="A1:J22"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="13.6640625" customWidth="1"/>
-    <col min="2" max="2" width="18.77734375" customWidth="1"/>
-    <col min="5" max="5" width="13.77734375" customWidth="1"/>
-    <col min="6" max="6" width="18" customWidth="1"/>
-    <col min="8" max="8" width="24.109375" customWidth="1"/>
-    <col min="9" max="9" width="20.33203125" customWidth="1"/>
-    <col min="11" max="11" width="15.77734375" customWidth="1"/>
-    <col min="12" max="12" width="13.21875" customWidth="1"/>
-    <col min="13" max="13" width="12.21875" customWidth="1"/>
+    <col min="1" max="1" width="13.7109375" customWidth="1"/>
+    <col min="2" max="2" width="18.7109375" customWidth="1"/>
+    <col min="3" max="3" width="22.140625" customWidth="1"/>
+    <col min="4" max="4" width="14.28515625" customWidth="1"/>
+    <col min="5" max="5" width="13.7109375" customWidth="1"/>
+    <col min="6" max="6" width="26.42578125" customWidth="1"/>
+    <col min="7" max="7" width="30.5703125" customWidth="1"/>
+    <col min="8" max="8" width="24.140625" customWidth="1"/>
+    <col min="9" max="9" width="20.28515625" customWidth="1"/>
+    <col min="11" max="11" width="15.7109375" customWidth="1"/>
+    <col min="12" max="12" width="13.28515625" customWidth="1"/>
+    <col min="13" max="13" width="12.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>1</v>
       </c>
@@ -1306,117 +1678,257 @@
         <v>64</v>
       </c>
     </row>
-    <row r="2" spans="1:9" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:9" ht="20.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>18</v>
       </c>
-      <c r="B2" s="6"/>
-      <c r="D2" s="1"/>
-      <c r="E2" s="1"/>
-      <c r="F2" s="6"/>
+      <c r="B2" s="6">
+        <v>46235.405555555553</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="D2" s="1">
+        <v>-23.551134000000001</v>
+      </c>
+      <c r="E2" s="1">
+        <v>-42.889713</v>
+      </c>
+      <c r="F2" s="6">
+        <v>46233.706250000003</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>66</v>
+      </c>
       <c r="H2" s="1"/>
       <c r="I2" s="1"/>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>16</v>
       </c>
-      <c r="B3" s="6"/>
-      <c r="D3" s="1"/>
-      <c r="E3" s="1"/>
-      <c r="F3" s="6"/>
+      <c r="B3" s="6">
+        <v>46235.405555555553</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="D3" s="1">
+        <v>-22.529060000000001</v>
+      </c>
+      <c r="E3" s="1">
+        <v>-40.045006000000001</v>
+      </c>
+      <c r="F3" s="6">
+        <v>46234.787499999999</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>67</v>
+      </c>
       <c r="H3" s="1"/>
       <c r="I3" s="1"/>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>17</v>
       </c>
-      <c r="B4" s="6"/>
-      <c r="D4" s="1"/>
-      <c r="E4" s="1"/>
-      <c r="F4" s="6"/>
+      <c r="B4" s="6">
+        <v>46235.405555555553</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="D4" s="1">
+        <v>-24.952517</v>
+      </c>
+      <c r="E4" s="1">
+        <v>-42.499732999999999</v>
+      </c>
+      <c r="F4" s="6">
+        <v>46232.570833333331</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>67</v>
+      </c>
       <c r="H4" s="1"/>
       <c r="I4" s="1"/>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>13</v>
       </c>
-      <c r="B5" s="6"/>
-      <c r="D5" s="1"/>
-      <c r="E5" s="1"/>
-      <c r="F5" s="6"/>
+      <c r="B5" s="6">
+        <v>46235.405555555553</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="D5" s="1">
+        <v>-22.384433999999999</v>
+      </c>
+      <c r="E5" s="1">
+        <v>-41.768687999999997</v>
+      </c>
+      <c r="F5" s="6">
+        <v>46235.400694444441</v>
+      </c>
+      <c r="G5" s="1" t="s">
+        <v>68</v>
+      </c>
       <c r="H5" s="1"/>
       <c r="I5" s="1"/>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>22</v>
       </c>
-      <c r="B6" s="6"/>
-      <c r="D6" s="1"/>
-      <c r="E6" s="1"/>
-      <c r="F6" s="6"/>
+      <c r="B6" s="6">
+        <v>46235.405555555553</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="D6" s="1">
+        <v>-23.319583999999999</v>
+      </c>
+      <c r="E6" s="1">
+        <v>-43.045639000000001</v>
+      </c>
+      <c r="F6" s="6">
+        <v>46234.691666666666</v>
+      </c>
+      <c r="G6" s="1" t="s">
+        <v>66</v>
+      </c>
       <c r="H6" s="1"/>
       <c r="I6" s="1"/>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>20</v>
       </c>
-      <c r="B7" s="6"/>
-      <c r="D7" s="1"/>
-      <c r="E7" s="1"/>
-      <c r="F7" s="6"/>
+      <c r="B7" s="6">
+        <v>46235.405555555553</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="D7" s="1">
+        <v>-21.261973999999999</v>
+      </c>
+      <c r="E7" s="1">
+        <v>-40.043221000000003</v>
+      </c>
+      <c r="F7" s="6">
+        <v>46234.672222222223</v>
+      </c>
+      <c r="G7" s="1" t="s">
+        <v>69</v>
+      </c>
       <c r="H7" s="1"/>
       <c r="I7" s="1"/>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>21</v>
       </c>
-      <c r="B8" s="6"/>
-      <c r="D8" s="1"/>
-      <c r="E8" s="1"/>
-      <c r="F8" s="6"/>
+      <c r="B8" s="6">
+        <v>46235.405555555553</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="D8" s="1">
+        <v>-22.872579999999999</v>
+      </c>
+      <c r="E8" s="1">
+        <v>-43.125988</v>
+      </c>
+      <c r="F8" s="6">
+        <v>46235.40347222222</v>
+      </c>
+      <c r="G8" s="1" t="s">
+        <v>67</v>
+      </c>
       <c r="H8" s="1"/>
       <c r="I8" s="1"/>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>42</v>
       </c>
-      <c r="B9" s="6"/>
-      <c r="D9" s="1"/>
-      <c r="E9" s="1"/>
-      <c r="F9" s="6"/>
+      <c r="B9" s="6">
+        <v>46235.405555555553</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="D9" s="1">
+        <v>-25.126089</v>
+      </c>
+      <c r="E9" s="1">
+        <v>-43.074348000000001</v>
+      </c>
+      <c r="F9" s="6">
+        <v>46232.600694444445</v>
+      </c>
+      <c r="G9" s="1" t="s">
+        <v>66</v>
+      </c>
       <c r="H9" s="1"/>
       <c r="I9" s="1"/>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>15</v>
       </c>
-      <c r="B10" s="6"/>
-      <c r="D10" s="1"/>
-      <c r="E10" s="1"/>
-      <c r="F10" s="6"/>
+      <c r="B10" s="6">
+        <v>46235.405555555553</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="D10" s="1">
+        <v>-22.845222</v>
+      </c>
+      <c r="E10" s="1">
+        <v>-43.136353</v>
+      </c>
+      <c r="F10" s="6">
+        <v>46235.404166666667</v>
+      </c>
+      <c r="G10" s="1" t="s">
+        <v>65</v>
+      </c>
       <c r="H10" s="1"/>
       <c r="I10" s="1"/>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>40</v>
       </c>
-      <c r="B11" s="6"/>
-      <c r="D11" s="1"/>
-      <c r="E11" s="1"/>
-      <c r="F11" s="6"/>
+      <c r="B11" s="6">
+        <v>46235.405555555553</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="D11" s="1">
+        <v>-22.851897999999998</v>
+      </c>
+      <c r="E11" s="1">
+        <v>-43.150620000000004</v>
+      </c>
+      <c r="F11" s="6">
+        <v>46235.40347222222</v>
+      </c>
+      <c r="G11" s="1" t="s">
+        <v>65</v>
+      </c>
       <c r="H11" s="1"/>
       <c r="I11" s="1"/>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>41</v>
       </c>
@@ -1428,7 +1940,7 @@
       <c r="H12" s="1"/>
       <c r="I12" s="1"/>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>14</v>
       </c>
@@ -1440,7 +1952,7 @@
       <c r="H13" s="1"/>
       <c r="I13" s="1"/>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>43</v>
       </c>
@@ -1452,7 +1964,7 @@
       <c r="H14" s="1"/>
       <c r="I14" s="1"/>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>19</v>
       </c>
@@ -1464,19 +1976,19 @@
       <c r="H15" s="1"/>
       <c r="I15" s="1"/>
     </row>
-    <row r="18" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="18" spans="10:10" x14ac:dyDescent="0.25">
       <c r="J18" s="1"/>
     </row>
-    <row r="19" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="19" spans="10:10" x14ac:dyDescent="0.25">
       <c r="J19" s="1"/>
     </row>
-    <row r="20" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="20" spans="10:10" x14ac:dyDescent="0.25">
       <c r="J20" s="1"/>
     </row>
-    <row r="21" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="21" spans="10:10" x14ac:dyDescent="0.25">
       <c r="J21" s="1"/>
     </row>
-    <row r="22" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="22" spans="10:10" x14ac:dyDescent="0.25">
       <c r="J22" s="1"/>
     </row>
   </sheetData>
@@ -1488,21 +2000,21 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FC0244D8-3EC3-425D-A328-9D6A0DAB3C45}">
   <dimension ref="A1:N18"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="17" customWidth="1"/>
-    <col min="2" max="2" width="18.21875" style="5" customWidth="1"/>
-    <col min="3" max="3" width="18.5546875" customWidth="1"/>
+    <col min="1" max="1" width="26.140625" customWidth="1"/>
+    <col min="2" max="2" width="18.28515625" style="5" customWidth="1"/>
+    <col min="3" max="3" width="18.5703125" customWidth="1"/>
     <col min="4" max="4" width="11" customWidth="1"/>
-    <col min="5" max="5" width="19.33203125" customWidth="1"/>
-    <col min="6" max="6" width="18.6640625" style="5" customWidth="1"/>
-    <col min="7" max="7" width="15.88671875" customWidth="1"/>
-    <col min="8" max="8" width="22.33203125" customWidth="1"/>
-    <col min="9" max="9" width="23.109375" customWidth="1"/>
-    <col min="11" max="11" width="14.5546875" customWidth="1"/>
+    <col min="5" max="5" width="19.28515625" customWidth="1"/>
+    <col min="6" max="6" width="18.7109375" style="5" customWidth="1"/>
+    <col min="7" max="7" width="15.85546875" customWidth="1"/>
+    <col min="8" max="8" width="22.28515625" customWidth="1"/>
+    <col min="9" max="9" width="23.140625" customWidth="1"/>
+    <col min="11" max="11" width="14.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>2</v>
       </c>
@@ -1528,202 +2040,380 @@
         <v>64</v>
       </c>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>30</v>
       </c>
-      <c r="B2" s="6"/>
+      <c r="B2" s="6">
+        <v>46235.40347222222</v>
+      </c>
       <c r="C2" s="1"/>
-      <c r="D2" s="1"/>
-      <c r="E2" s="1"/>
-      <c r="F2" s="6"/>
-      <c r="H2" s="1"/>
+      <c r="D2" s="1">
+        <v>-22.855374999999999</v>
+      </c>
+      <c r="E2" s="1">
+        <v>-43.144660999999999</v>
+      </c>
+      <c r="F2" s="6">
+        <v>46235.4</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>65</v>
+      </c>
       <c r="I2" s="1"/>
     </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>27</v>
       </c>
-      <c r="B3" s="6"/>
+      <c r="B3" s="6">
+        <v>46235.40347222222</v>
+      </c>
       <c r="C3" s="1"/>
-      <c r="D3" s="1"/>
-      <c r="E3" s="1"/>
-      <c r="F3" s="6"/>
-      <c r="H3" s="1"/>
+      <c r="D3" s="1">
+        <v>-23.896916999999998</v>
+      </c>
+      <c r="E3" s="1">
+        <v>-42.725639000000001</v>
+      </c>
+      <c r="F3" s="6">
+        <v>46235.388888888891</v>
+      </c>
+      <c r="H3" s="1" t="s">
+        <v>66</v>
+      </c>
       <c r="I3" s="1"/>
     </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>31</v>
       </c>
-      <c r="B4" s="6"/>
+      <c r="B4" s="6">
+        <v>46235.40347222222</v>
+      </c>
       <c r="C4" s="1"/>
-      <c r="D4" s="1"/>
-      <c r="E4" s="1"/>
-      <c r="F4" s="6"/>
-      <c r="H4" s="1"/>
+      <c r="D4" s="1">
+        <v>-21.863904999999999</v>
+      </c>
+      <c r="E4" s="1">
+        <v>-41.016941000000003</v>
+      </c>
+      <c r="F4" s="6">
+        <v>46235.400694444441</v>
+      </c>
+      <c r="H4" s="1" t="s">
+        <v>68</v>
+      </c>
       <c r="I4" s="1"/>
     </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>26</v>
       </c>
-      <c r="B5" s="6"/>
+      <c r="B5" s="6">
+        <v>46235.40347222222</v>
+      </c>
       <c r="C5" s="1"/>
-      <c r="D5" s="1"/>
-      <c r="E5" s="1"/>
-      <c r="F5" s="6"/>
-      <c r="H5" s="1"/>
+      <c r="D5" s="1">
+        <v>-23.387266</v>
+      </c>
+      <c r="E5" s="1">
+        <v>-42.956206999999999</v>
+      </c>
+      <c r="F5" s="6">
+        <v>46233.78402777778</v>
+      </c>
+      <c r="H5" s="1" t="s">
+        <v>66</v>
+      </c>
       <c r="I5" s="1"/>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>52</v>
       </c>
-      <c r="B6" s="6"/>
+      <c r="B6" s="6">
+        <v>46235.40347222222</v>
+      </c>
       <c r="C6" s="1"/>
-      <c r="D6" s="1"/>
-      <c r="E6" s="1"/>
-      <c r="F6" s="6"/>
-      <c r="H6" s="1"/>
+      <c r="D6" s="1">
+        <v>-22.451302999999999</v>
+      </c>
+      <c r="E6" s="1">
+        <v>-40.411659</v>
+      </c>
+      <c r="F6" s="6">
+        <v>46235.117361111108</v>
+      </c>
+      <c r="H6" s="1" t="s">
+        <v>69</v>
+      </c>
       <c r="I6" s="1"/>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>54</v>
       </c>
-      <c r="B7" s="6"/>
+      <c r="B7" s="6">
+        <v>46235.40347222222</v>
+      </c>
       <c r="C7" s="1"/>
-      <c r="D7" s="1"/>
-      <c r="E7" s="1"/>
-      <c r="F7" s="6"/>
-      <c r="H7" s="1"/>
+      <c r="D7" s="1">
+        <v>-23.084102999999999</v>
+      </c>
+      <c r="E7" s="1">
+        <v>-42.557158999999999</v>
+      </c>
+      <c r="F7" s="6">
+        <v>46235.401388888888</v>
+      </c>
+      <c r="H7" s="1" t="s">
+        <v>66</v>
+      </c>
       <c r="I7" s="1"/>
     </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>34</v>
       </c>
-      <c r="B8" s="6"/>
-      <c r="D8" s="1"/>
-      <c r="E8" s="1"/>
-      <c r="H8" s="1"/>
+      <c r="B8" s="6">
+        <v>46235.40347222222</v>
+      </c>
+      <c r="C8" s="1"/>
+      <c r="D8" s="1">
+        <v>-21.96414</v>
+      </c>
+      <c r="E8" s="1">
+        <v>-39.826087999999999</v>
+      </c>
+      <c r="F8" s="6">
+        <v>46235.369444444441</v>
+      </c>
+      <c r="H8" s="1" t="s">
+        <v>67</v>
+      </c>
       <c r="I8" s="1"/>
     </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>55</v>
       </c>
-      <c r="B9" s="6"/>
+      <c r="B9" s="6">
+        <v>46235.40347222222</v>
+      </c>
       <c r="C9" s="1"/>
-      <c r="D9" s="1"/>
-      <c r="E9" s="1"/>
-      <c r="F9" s="6"/>
-      <c r="H9" s="1"/>
+      <c r="D9" s="1">
+        <v>-21.862418999999999</v>
+      </c>
+      <c r="E9" s="1">
+        <v>-41.017845000000001</v>
+      </c>
+      <c r="F9" s="6">
+        <v>46235.402083333334</v>
+      </c>
+      <c r="H9" s="1" t="s">
+        <v>67</v>
+      </c>
       <c r="I9" s="1"/>
     </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>28</v>
       </c>
-      <c r="B10" s="6"/>
+      <c r="B10" s="6">
+        <v>46235.40347222222</v>
+      </c>
       <c r="C10" s="1"/>
-      <c r="D10" s="1"/>
-      <c r="E10" s="1"/>
-      <c r="F10" s="6"/>
-      <c r="H10" s="1"/>
+      <c r="D10" s="1">
+        <v>-22.396485999999999</v>
+      </c>
+      <c r="E10" s="1">
+        <v>-40.109240999999997</v>
+      </c>
+      <c r="F10" s="6">
+        <v>46235.306250000001</v>
+      </c>
+      <c r="H10" s="1" t="s">
+        <v>67</v>
+      </c>
       <c r="I10" s="1"/>
     </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>56</v>
       </c>
-      <c r="B11" s="6"/>
+      <c r="B11" s="6">
+        <v>46235.40347222222</v>
+      </c>
       <c r="C11" s="1"/>
-      <c r="D11" s="1"/>
-      <c r="E11" s="1"/>
-      <c r="F11" s="6"/>
-      <c r="H11" s="1"/>
+      <c r="D11" s="1">
+        <v>-21.93272</v>
+      </c>
+      <c r="E11" s="1">
+        <v>-39.784393000000001</v>
+      </c>
+      <c r="F11" s="6">
+        <v>46234.636111111111</v>
+      </c>
+      <c r="H11" s="1" t="s">
+        <v>67</v>
+      </c>
       <c r="I11" s="1"/>
     </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>33</v>
       </c>
-      <c r="B12" s="6"/>
+      <c r="B12" s="6">
+        <v>46235.400694444441</v>
+      </c>
       <c r="C12" s="1"/>
-      <c r="D12" s="1"/>
-      <c r="E12" s="1"/>
-      <c r="F12" s="6"/>
-      <c r="H12" s="1"/>
+      <c r="D12" s="1">
+        <v>-22.859172999999998</v>
+      </c>
+      <c r="E12" s="1">
+        <v>-43.162827</v>
+      </c>
+      <c r="F12" s="6">
+        <v>46235.395833333336</v>
+      </c>
+      <c r="H12" s="1" t="s">
+        <v>65</v>
+      </c>
       <c r="I12" s="1"/>
       <c r="N12" s="1"/>
     </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>23</v>
       </c>
-      <c r="B13" s="6"/>
-      <c r="D13" s="1"/>
-      <c r="E13" s="1"/>
-      <c r="F13" s="6"/>
-      <c r="H13" s="1"/>
+      <c r="B13" s="6">
+        <v>46235.400694444441</v>
+      </c>
+      <c r="C13" s="1"/>
+      <c r="D13" s="1">
+        <v>-21.991858000000001</v>
+      </c>
+      <c r="E13" s="1">
+        <v>-40.755360000000003</v>
+      </c>
+      <c r="F13" s="6">
+        <v>46235.068055555559</v>
+      </c>
+      <c r="H13" s="1" t="s">
+        <v>66</v>
+      </c>
       <c r="I13" s="1"/>
       <c r="N13" s="1"/>
     </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>32</v>
       </c>
-      <c r="B14" s="6"/>
-      <c r="D14" s="1"/>
-      <c r="E14" s="1"/>
-      <c r="F14" s="6"/>
-      <c r="H14" s="1"/>
+      <c r="B14" s="6">
+        <v>46235.400694444441</v>
+      </c>
+      <c r="C14" s="1"/>
+      <c r="D14" s="1">
+        <v>-23.638178</v>
+      </c>
+      <c r="E14" s="1">
+        <v>-43.141171</v>
+      </c>
+      <c r="F14" s="6">
+        <v>46235.392361111109</v>
+      </c>
+      <c r="H14" s="1" t="s">
+        <v>66</v>
+      </c>
       <c r="I14" s="1"/>
     </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>24</v>
       </c>
-      <c r="B15" s="6"/>
-      <c r="D15" s="1"/>
-      <c r="E15" s="1"/>
-      <c r="F15" s="6"/>
-      <c r="H15" s="1"/>
+      <c r="B15" s="6">
+        <v>46235.400694444441</v>
+      </c>
+      <c r="C15" s="1"/>
+      <c r="D15" s="1">
+        <v>-22.862338999999999</v>
+      </c>
+      <c r="E15" s="1">
+        <v>-43.175773999999997</v>
+      </c>
+      <c r="F15" s="6">
+        <v>46235.397222222222</v>
+      </c>
+      <c r="H15" s="1" t="s">
+        <v>65</v>
+      </c>
       <c r="I15" s="1"/>
     </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>29</v>
       </c>
-      <c r="B16" s="6"/>
-      <c r="D16" s="1"/>
-      <c r="E16" s="1"/>
-      <c r="F16" s="6"/>
-      <c r="H16" s="1"/>
+      <c r="B16" s="6">
+        <v>46235.400694444441</v>
+      </c>
+      <c r="C16" s="1"/>
+      <c r="D16" s="1">
+        <v>-22.857548000000001</v>
+      </c>
+      <c r="E16" s="1">
+        <v>-43.166058</v>
+      </c>
+      <c r="F16" s="6">
+        <v>46235.395833333336</v>
+      </c>
+      <c r="H16" s="1" t="s">
+        <v>65</v>
+      </c>
       <c r="I16" s="1"/>
     </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>25</v>
       </c>
-      <c r="B17" s="6"/>
-      <c r="D17" s="1"/>
-      <c r="E17" s="1"/>
-      <c r="F17" s="6"/>
-      <c r="H17" s="1"/>
+      <c r="B17" s="6">
+        <v>46235.400694444441</v>
+      </c>
+      <c r="C17" s="1"/>
+      <c r="D17" s="1">
+        <v>-26.856745</v>
+      </c>
+      <c r="E17" s="1">
+        <v>-48.721401</v>
+      </c>
+      <c r="F17" s="6">
+        <v>46120.325694444444</v>
+      </c>
+      <c r="H17" s="1" t="s">
+        <v>67</v>
+      </c>
       <c r="I17" s="1"/>
     </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>53</v>
       </c>
-      <c r="B18" s="6"/>
-      <c r="D18" s="1"/>
-      <c r="E18" s="1"/>
-      <c r="F18" s="6"/>
-      <c r="H18" s="1"/>
+      <c r="B18" s="6">
+        <v>46235.400694444441</v>
+      </c>
+      <c r="C18" s="1"/>
+      <c r="D18" s="1">
+        <v>-23.373629000000001</v>
+      </c>
+      <c r="E18" s="1">
+        <v>-42.836627999999997</v>
+      </c>
+      <c r="F18" s="6">
+        <v>46233.893055555556</v>
+      </c>
+      <c r="H18" s="1" t="s">
+        <v>66</v>
+      </c>
       <c r="I18" s="1"/>
     </row>
   </sheetData>

--- a/dados/SURVEY_VESSELS/SURVEY_VESSELS_20260801_manha.xlsx
+++ b/dados/SURVEY_VESSELS/SURVEY_VESSELS_20260801_manha.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cefetrjbr-my.sharepoint.com/personal/12396387790_cefet-rj_br/Documents/Empresas e entrevistas/projeto logistica offshore/ofi/dados/SURVEY_VESSELS/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1028" documentId="8_{2FDA8D28-226B-473E-B58F-AB3C8EEAFC38}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7D6743E2-2F5F-4CAA-8B6B-32ADD4812534}"/>
+  <xr:revisionPtr revIDLastSave="1049" documentId="8_{2FDA8D28-226B-473E-B58F-AB3C8EEAFC38}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7E09B6DB-5340-44D7-A0AB-D39F33F0D2E0}"/>
   <bookViews>
-    <workbookView xWindow="-105" yWindow="0" windowWidth="14610" windowHeight="15585" activeTab="1" xr2:uid="{FAEFD476-B005-4995-A964-6D919B2AA8E5}"/>
+    <workbookView xWindow="-105" yWindow="0" windowWidth="14610" windowHeight="15585" activeTab="3" xr2:uid="{FAEFD476-B005-4995-A964-6D919B2AA8E5}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="230" uniqueCount="101">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="206" uniqueCount="72">
   <si>
     <t>cbo</t>
   </si>
@@ -254,97 +254,10 @@
     <t>Restricted Manoeuvrability</t>
   </si>
   <si>
-    <t>BRAM ATLAS</t>
-  </si>
-  <si>
-    <t>BRAM BAHIA</t>
-  </si>
-  <si>
-    <t>BRAM BELEM</t>
-  </si>
-  <si>
-    <t>BRAM BRASIL</t>
-  </si>
-  <si>
-    <t>BRAM BRASILIA</t>
-  </si>
-  <si>
-    <t>BRAM BRAVO</t>
-  </si>
-  <si>
-    <t>BRAM BREEZE</t>
-  </si>
-  <si>
-    <t>BRAM BUCK</t>
-  </si>
-  <si>
-    <t>BRAM BUZIOS</t>
-  </si>
-  <si>
-    <t>BRAM HERO</t>
-  </si>
-  <si>
-    <t>CBO ALESSANDRA</t>
-  </si>
-  <si>
-    <t>CBO ALIANCA</t>
-  </si>
-  <si>
-    <t>CBO ANITA</t>
-  </si>
-  <si>
-    <t>CBO ARPOADOR</t>
-  </si>
-  <si>
-    <t>CBO CAMPOS</t>
-  </si>
-  <si>
-    <t>CBO CAROLINA</t>
-  </si>
-  <si>
-    <t>CBO COPACABANA</t>
-  </si>
-  <si>
-    <t>CBO ENERGY</t>
-  </si>
-  <si>
-    <t>CBO FLAMENGO</t>
-  </si>
-  <si>
-    <t>CBO IPANEMA</t>
-  </si>
-  <si>
-    <t>CBO ISABELLA</t>
-  </si>
-  <si>
-    <t>CBO ITAJAI</t>
-  </si>
-  <si>
-    <t>CBO MANOELLA</t>
-  </si>
-  <si>
-    <t>CBO OCEANA</t>
-  </si>
-  <si>
-    <t>CBO RENATA</t>
-  </si>
-  <si>
-    <t>CBO RIO</t>
-  </si>
-  <si>
     <t>Class B</t>
   </si>
   <si>
-    <t>CBO SUPPORTER</t>
-  </si>
-  <si>
-    <t>CBO VITORIA</t>
-  </si>
-  <si>
-    <t>CBO WAVE</t>
-  </si>
-  <si>
-    <t>CBO WISER</t>
+    <t>Underway</t>
   </si>
 </sst>
 </file>
@@ -1039,12 +952,12 @@
   <dimension ref="A1:O27"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="16.42578125" customWidth="1"/>
+    <col min="1" max="1" width="18.7109375" customWidth="1"/>
     <col min="2" max="2" width="21.5703125" customWidth="1"/>
-    <col min="3" max="3" width="15.140625" customWidth="1"/>
+    <col min="3" max="3" width="25.5703125" customWidth="1"/>
     <col min="6" max="6" width="20.7109375" customWidth="1"/>
-    <col min="7" max="7" width="12.42578125" customWidth="1"/>
-    <col min="8" max="8" width="23.28515625" customWidth="1"/>
+    <col min="7" max="7" width="16.7109375" customWidth="1"/>
+    <col min="8" max="8" width="27.7109375" customWidth="1"/>
     <col min="11" max="11" width="21" customWidth="1"/>
     <col min="13" max="13" width="14.140625" customWidth="1"/>
     <col min="14" max="14" width="14.42578125" customWidth="1"/>
@@ -1083,9 +996,7 @@
       <c r="B2" s="6">
         <v>46235.407638888886</v>
       </c>
-      <c r="C2" s="1" t="s">
-        <v>80</v>
-      </c>
+      <c r="C2" s="1"/>
       <c r="D2" s="1">
         <v>-22.843443000000001</v>
       </c>
@@ -1095,10 +1006,9 @@
       <c r="F2" s="6">
         <v>46235.405555555553</v>
       </c>
-      <c r="G2" s="1" t="s">
+      <c r="H2" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="H2" s="1"/>
       <c r="I2" s="1"/>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.25">
@@ -1108,9 +1018,7 @@
       <c r="B3" s="6">
         <v>46235.407638888886</v>
       </c>
-      <c r="C3" s="1" t="s">
-        <v>81</v>
-      </c>
+      <c r="C3" s="1"/>
       <c r="D3" s="1">
         <v>-25.617207000000001</v>
       </c>
@@ -1120,10 +1028,9 @@
       <c r="F3" s="6">
         <v>46232.576388888891</v>
       </c>
-      <c r="G3" s="1" t="s">
+      <c r="H3" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="H3" s="1"/>
       <c r="I3" s="1"/>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
@@ -1133,9 +1040,7 @@
       <c r="B4" s="6">
         <v>46235.407638888886</v>
       </c>
-      <c r="C4" s="1" t="s">
-        <v>82</v>
-      </c>
+      <c r="C4" s="1"/>
       <c r="D4" s="1">
         <v>-23.513812999999999</v>
       </c>
@@ -1145,10 +1050,9 @@
       <c r="F4" s="6">
         <v>46235.086805555555</v>
       </c>
-      <c r="G4" s="1" t="s">
+      <c r="H4" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="H4" s="1"/>
       <c r="I4" s="1"/>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.25">
@@ -1158,9 +1062,7 @@
       <c r="B5" s="6">
         <v>46235.407638888886</v>
       </c>
-      <c r="C5" s="1" t="s">
-        <v>83</v>
-      </c>
+      <c r="C5" s="1"/>
       <c r="D5" s="1">
         <v>-22.881622</v>
       </c>
@@ -1170,10 +1072,9 @@
       <c r="F5" s="6">
         <v>46235.404861111114</v>
       </c>
-      <c r="G5" s="1" t="s">
+      <c r="H5" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="H5" s="1"/>
       <c r="I5" s="1"/>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.25">
@@ -1183,9 +1084,7 @@
       <c r="B6" s="6">
         <v>46235.407638888886</v>
       </c>
-      <c r="C6" s="1" t="s">
-        <v>84</v>
-      </c>
+      <c r="C6" s="1"/>
       <c r="D6" s="1">
         <v>-22.864473</v>
       </c>
@@ -1195,10 +1094,9 @@
       <c r="F6" s="6">
         <v>44390.56527777778</v>
       </c>
-      <c r="G6" s="1" t="s">
+      <c r="H6" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="H6" s="1"/>
       <c r="I6" s="1"/>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.25">
@@ -1208,9 +1106,7 @@
       <c r="B7" s="6">
         <v>46235.407638888886</v>
       </c>
-      <c r="C7" s="1" t="s">
-        <v>85</v>
-      </c>
+      <c r="C7" s="1"/>
       <c r="D7" s="1">
         <v>-23.421261000000001</v>
       </c>
@@ -1220,10 +1116,9 @@
       <c r="F7" s="6">
         <v>46235.394444444442</v>
       </c>
-      <c r="G7" s="1" t="s">
+      <c r="H7" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="H7" s="1"/>
       <c r="I7" s="1"/>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.25">
@@ -1233,9 +1128,7 @@
       <c r="B8" s="6">
         <v>46235.407638888886</v>
       </c>
-      <c r="C8" s="1" t="s">
-        <v>86</v>
-      </c>
+      <c r="C8" s="1"/>
       <c r="D8" s="1">
         <v>-22.894600000000001</v>
       </c>
@@ -1245,10 +1138,9 @@
       <c r="F8" s="6">
         <v>46235.404861111114</v>
       </c>
-      <c r="G8" s="1" t="s">
+      <c r="H8" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="H8" s="1"/>
       <c r="I8" s="1"/>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.25">
@@ -1258,9 +1150,7 @@
       <c r="B9" s="6">
         <v>46235.407638888886</v>
       </c>
-      <c r="C9" s="1" t="s">
-        <v>87</v>
-      </c>
+      <c r="C9" s="1"/>
       <c r="D9" s="1">
         <v>-23.313922999999999</v>
       </c>
@@ -1270,10 +1160,9 @@
       <c r="F9" s="6">
         <v>46235.061111111114</v>
       </c>
-      <c r="G9" s="1" t="s">
+      <c r="H9" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="H9" s="1"/>
       <c r="I9" s="1"/>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.25">
@@ -1283,9 +1172,7 @@
       <c r="B10" s="6">
         <v>46235.407638888886</v>
       </c>
-      <c r="C10" s="1" t="s">
-        <v>88</v>
-      </c>
+      <c r="C10" s="1"/>
       <c r="D10" s="1">
         <v>-21.978467999999999</v>
       </c>
@@ -1295,10 +1182,9 @@
       <c r="F10" s="6">
         <v>46235.177083333336</v>
       </c>
-      <c r="G10" s="1" t="s">
+      <c r="H10" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="H10" s="1"/>
       <c r="I10" s="1"/>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.25">
@@ -1308,9 +1194,7 @@
       <c r="B11" s="6">
         <v>46235.407638888886</v>
       </c>
-      <c r="C11" s="1" t="s">
-        <v>89</v>
-      </c>
+      <c r="C11" s="1"/>
       <c r="D11" s="1">
         <v>-23.563127999999999</v>
       </c>
@@ -1320,10 +1204,9 @@
       <c r="F11" s="6">
         <v>46235.114583333336</v>
       </c>
-      <c r="G11" s="1" t="s">
+      <c r="H11" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="H11" s="1"/>
       <c r="I11" s="1"/>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.25">
@@ -1333,9 +1216,7 @@
       <c r="B12" s="6">
         <v>46235.418055555558</v>
       </c>
-      <c r="C12" s="1" t="s">
-        <v>90</v>
-      </c>
+      <c r="C12" s="1"/>
       <c r="D12" s="1">
         <v>-22.894380999999999</v>
       </c>
@@ -1345,10 +1226,9 @@
       <c r="F12" s="6">
         <v>46235.413194444445</v>
       </c>
-      <c r="G12" s="1" t="s">
+      <c r="H12" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="H12" s="1"/>
       <c r="I12" s="1"/>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.25">
@@ -1358,9 +1238,7 @@
       <c r="B13" s="6">
         <v>46235.418055555558</v>
       </c>
-      <c r="C13" s="1" t="s">
-        <v>91</v>
-      </c>
+      <c r="C13" s="1"/>
       <c r="D13" s="1">
         <v>-22.836293999999999</v>
       </c>
@@ -1370,10 +1248,9 @@
       <c r="F13" s="6">
         <v>46235.416666666664</v>
       </c>
-      <c r="G13" s="1" t="s">
+      <c r="H13" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="H13" s="1"/>
       <c r="I13" s="1"/>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.25">
@@ -1383,9 +1260,7 @@
       <c r="B14" s="6">
         <v>46235.418055555558</v>
       </c>
-      <c r="C14" s="1" t="s">
-        <v>92</v>
-      </c>
+      <c r="C14" s="1"/>
       <c r="D14" s="1">
         <v>-25.20393</v>
       </c>
@@ -1395,10 +1270,9 @@
       <c r="F14" s="6">
         <v>46232.605555555558</v>
       </c>
-      <c r="G14" s="1" t="s">
+      <c r="H14" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="H14" s="1"/>
       <c r="I14" s="1"/>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.25">
@@ -1408,9 +1282,7 @@
       <c r="B15" s="6">
         <v>46235.418055555558</v>
       </c>
-      <c r="C15" s="1" t="s">
-        <v>93</v>
-      </c>
+      <c r="C15" s="1"/>
       <c r="D15" s="1">
         <v>-22.895192999999999</v>
       </c>
@@ -1420,10 +1292,9 @@
       <c r="F15" s="6">
         <v>46235.416666666664</v>
       </c>
-      <c r="G15" s="1" t="s">
+      <c r="H15" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="H15" s="1"/>
       <c r="I15" s="1"/>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.25">
@@ -1433,9 +1304,7 @@
       <c r="B16" s="6">
         <v>46235.418055555558</v>
       </c>
-      <c r="C16" s="1" t="s">
-        <v>94</v>
-      </c>
+      <c r="C16" s="1"/>
       <c r="D16" s="1">
         <v>-21.214157</v>
       </c>
@@ -1445,10 +1314,9 @@
       <c r="F16" s="6">
         <v>46234.745138888888</v>
       </c>
-      <c r="G16" s="1" t="s">
+      <c r="H16" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="H16" s="1"/>
       <c r="I16" s="1"/>
     </row>
     <row r="17" spans="1:15" x14ac:dyDescent="0.25">
@@ -1458,9 +1326,7 @@
       <c r="B17" s="6">
         <v>46235.418055555558</v>
       </c>
-      <c r="C17" s="1" t="s">
-        <v>95</v>
-      </c>
+      <c r="C17" s="1"/>
       <c r="D17" s="1">
         <v>-30.372271999999999</v>
       </c>
@@ -1470,10 +1336,9 @@
       <c r="F17" s="6">
         <v>44677.811111111114</v>
       </c>
-      <c r="G17" s="1" t="s">
-        <v>96</v>
-      </c>
-      <c r="H17" s="1"/>
+      <c r="H17" s="1" t="s">
+        <v>70</v>
+      </c>
       <c r="I17" s="1"/>
     </row>
     <row r="18" spans="1:15" x14ac:dyDescent="0.25">
@@ -1483,9 +1348,7 @@
       <c r="B18" s="6">
         <v>46235.418055555558</v>
       </c>
-      <c r="C18" s="1" t="s">
-        <v>97</v>
-      </c>
+      <c r="C18" s="1"/>
       <c r="D18" s="1">
         <v>-23.395835999999999</v>
       </c>
@@ -1495,10 +1358,9 @@
       <c r="F18" s="6">
         <v>46235.179861111108</v>
       </c>
-      <c r="G18" s="1" t="s">
+      <c r="H18" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="H18" s="1"/>
       <c r="I18" s="1"/>
     </row>
     <row r="19" spans="1:15" x14ac:dyDescent="0.25">
@@ -1508,9 +1370,7 @@
       <c r="B19" s="6">
         <v>46235.418055555558</v>
       </c>
-      <c r="C19" s="1" t="s">
-        <v>98</v>
-      </c>
+      <c r="C19" s="1"/>
       <c r="D19" s="1">
         <v>-22.864526999999999</v>
       </c>
@@ -1520,10 +1380,9 @@
       <c r="F19" s="6">
         <v>45839.576388888891</v>
       </c>
-      <c r="G19" s="1" t="s">
+      <c r="H19" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="H19" s="1"/>
       <c r="I19" s="1"/>
     </row>
     <row r="20" spans="1:15" x14ac:dyDescent="0.25">
@@ -1533,9 +1392,7 @@
       <c r="B20" s="6">
         <v>46235.418055555558</v>
       </c>
-      <c r="C20" s="1" t="s">
-        <v>99</v>
-      </c>
+      <c r="C20" s="1"/>
       <c r="D20" s="1">
         <v>-24.652591999999999</v>
       </c>
@@ -1545,10 +1402,9 @@
       <c r="F20" s="6">
         <v>46232.638888888891</v>
       </c>
-      <c r="G20" s="1" t="s">
+      <c r="H20" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="H20" s="1"/>
       <c r="I20" s="1"/>
     </row>
     <row r="21" spans="1:15" x14ac:dyDescent="0.25">
@@ -1558,9 +1414,7 @@
       <c r="B21" s="6">
         <v>46235.418055555558</v>
       </c>
-      <c r="C21" s="1" t="s">
-        <v>100</v>
-      </c>
+      <c r="C21" s="1"/>
       <c r="D21" s="1">
         <v>-25.491667</v>
       </c>
@@ -1570,22 +1424,31 @@
       <c r="F21" s="6">
         <v>46233.682638888888</v>
       </c>
-      <c r="G21" s="1" t="s">
+      <c r="H21" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="H21" s="1"/>
       <c r="I21" s="1"/>
     </row>
     <row r="22" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>12</v>
       </c>
-      <c r="B22" s="6"/>
+      <c r="B22" s="6">
+        <v>46235.420138888891</v>
+      </c>
       <c r="C22" s="1"/>
-      <c r="D22" s="1"/>
-      <c r="E22" s="1"/>
-      <c r="F22" s="6"/>
-      <c r="H22" s="1"/>
+      <c r="D22" s="1">
+        <v>-22.852388000000001</v>
+      </c>
+      <c r="E22" s="1">
+        <v>-43.139831999999998</v>
+      </c>
+      <c r="F22" s="6">
+        <v>46235.416666666664</v>
+      </c>
+      <c r="H22" s="1" t="s">
+        <v>65</v>
+      </c>
       <c r="J22" s="1"/>
       <c r="O22" s="4"/>
     </row>
@@ -1593,12 +1456,22 @@
       <c r="A23" t="s">
         <v>8</v>
       </c>
-      <c r="B23" s="6"/>
+      <c r="B23" s="6">
+        <v>46235.420138888891</v>
+      </c>
       <c r="C23" s="1"/>
-      <c r="D23" s="1"/>
-      <c r="E23" s="1"/>
-      <c r="F23" s="6"/>
-      <c r="H23" s="1"/>
+      <c r="D23" s="1">
+        <v>-23.017219999999998</v>
+      </c>
+      <c r="E23" s="1">
+        <v>-43.069159999999997</v>
+      </c>
+      <c r="F23" s="6">
+        <v>46235.418055555558</v>
+      </c>
+      <c r="H23" s="1" t="s">
+        <v>71</v>
+      </c>
       <c r="J23" s="1"/>
     </row>
     <row r="24" spans="1:15" x14ac:dyDescent="0.25">
@@ -1645,7 +1518,7 @@
     <col min="5" max="5" width="13.7109375" customWidth="1"/>
     <col min="6" max="6" width="26.42578125" customWidth="1"/>
     <col min="7" max="7" width="30.5703125" customWidth="1"/>
-    <col min="8" max="8" width="24.140625" customWidth="1"/>
+    <col min="8" max="8" width="29.42578125" customWidth="1"/>
     <col min="9" max="9" width="20.28515625" customWidth="1"/>
     <col min="11" max="11" width="15.7109375" customWidth="1"/>
     <col min="12" max="12" width="13.28515625" customWidth="1"/>
@@ -1685,9 +1558,7 @@
       <c r="B2" s="6">
         <v>46235.405555555553</v>
       </c>
-      <c r="C2" s="1" t="s">
-        <v>70</v>
-      </c>
+      <c r="C2" s="1"/>
       <c r="D2" s="1">
         <v>-23.551134000000001</v>
       </c>
@@ -1697,10 +1568,9 @@
       <c r="F2" s="6">
         <v>46233.706250000003</v>
       </c>
-      <c r="G2" s="1" t="s">
+      <c r="H2" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="H2" s="1"/>
       <c r="I2" s="1"/>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.25">
@@ -1710,9 +1580,7 @@
       <c r="B3" s="6">
         <v>46235.405555555553</v>
       </c>
-      <c r="C3" s="1" t="s">
-        <v>71</v>
-      </c>
+      <c r="C3" s="1"/>
       <c r="D3" s="1">
         <v>-22.529060000000001</v>
       </c>
@@ -1722,10 +1590,9 @@
       <c r="F3" s="6">
         <v>46234.787499999999</v>
       </c>
-      <c r="G3" s="1" t="s">
+      <c r="H3" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="H3" s="1"/>
       <c r="I3" s="1"/>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
@@ -1735,9 +1602,7 @@
       <c r="B4" s="6">
         <v>46235.405555555553</v>
       </c>
-      <c r="C4" s="1" t="s">
-        <v>72</v>
-      </c>
+      <c r="C4" s="1"/>
       <c r="D4" s="1">
         <v>-24.952517</v>
       </c>
@@ -1747,10 +1612,9 @@
       <c r="F4" s="6">
         <v>46232.570833333331</v>
       </c>
-      <c r="G4" s="1" t="s">
+      <c r="H4" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="H4" s="1"/>
       <c r="I4" s="1"/>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.25">
@@ -1760,9 +1624,7 @@
       <c r="B5" s="6">
         <v>46235.405555555553</v>
       </c>
-      <c r="C5" s="1" t="s">
-        <v>73</v>
-      </c>
+      <c r="C5" s="1"/>
       <c r="D5" s="1">
         <v>-22.384433999999999</v>
       </c>
@@ -1772,10 +1634,9 @@
       <c r="F5" s="6">
         <v>46235.400694444441</v>
       </c>
-      <c r="G5" s="1" t="s">
+      <c r="H5" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="H5" s="1"/>
       <c r="I5" s="1"/>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.25">
@@ -1785,9 +1646,7 @@
       <c r="B6" s="6">
         <v>46235.405555555553</v>
       </c>
-      <c r="C6" s="1" t="s">
-        <v>74</v>
-      </c>
+      <c r="C6" s="1"/>
       <c r="D6" s="1">
         <v>-23.319583999999999</v>
       </c>
@@ -1797,10 +1656,9 @@
       <c r="F6" s="6">
         <v>46234.691666666666</v>
       </c>
-      <c r="G6" s="1" t="s">
+      <c r="H6" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="H6" s="1"/>
       <c r="I6" s="1"/>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.25">
@@ -1810,9 +1668,7 @@
       <c r="B7" s="6">
         <v>46235.405555555553</v>
       </c>
-      <c r="C7" s="1" t="s">
-        <v>75</v>
-      </c>
+      <c r="C7" s="1"/>
       <c r="D7" s="1">
         <v>-21.261973999999999</v>
       </c>
@@ -1822,10 +1678,9 @@
       <c r="F7" s="6">
         <v>46234.672222222223</v>
       </c>
-      <c r="G7" s="1" t="s">
+      <c r="H7" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="H7" s="1"/>
       <c r="I7" s="1"/>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.25">
@@ -1835,9 +1690,7 @@
       <c r="B8" s="6">
         <v>46235.405555555553</v>
       </c>
-      <c r="C8" s="1" t="s">
-        <v>76</v>
-      </c>
+      <c r="C8" s="1"/>
       <c r="D8" s="1">
         <v>-22.872579999999999</v>
       </c>
@@ -1847,10 +1700,9 @@
       <c r="F8" s="6">
         <v>46235.40347222222</v>
       </c>
-      <c r="G8" s="1" t="s">
+      <c r="H8" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="H8" s="1"/>
       <c r="I8" s="1"/>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.25">
@@ -1860,9 +1712,7 @@
       <c r="B9" s="6">
         <v>46235.405555555553</v>
       </c>
-      <c r="C9" s="1" t="s">
-        <v>77</v>
-      </c>
+      <c r="C9" s="1"/>
       <c r="D9" s="1">
         <v>-25.126089</v>
       </c>
@@ -1872,10 +1722,9 @@
       <c r="F9" s="6">
         <v>46232.600694444445</v>
       </c>
-      <c r="G9" s="1" t="s">
+      <c r="H9" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="H9" s="1"/>
       <c r="I9" s="1"/>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.25">
@@ -1885,9 +1734,7 @@
       <c r="B10" s="6">
         <v>46235.405555555553</v>
       </c>
-      <c r="C10" s="1" t="s">
-        <v>78</v>
-      </c>
+      <c r="C10" s="1"/>
       <c r="D10" s="1">
         <v>-22.845222</v>
       </c>
@@ -1897,10 +1744,9 @@
       <c r="F10" s="6">
         <v>46235.404166666667</v>
       </c>
-      <c r="G10" s="1" t="s">
+      <c r="H10" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="H10" s="1"/>
       <c r="I10" s="1"/>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.25">
@@ -1910,9 +1756,7 @@
       <c r="B11" s="6">
         <v>46235.405555555553</v>
       </c>
-      <c r="C11" s="1" t="s">
-        <v>79</v>
-      </c>
+      <c r="C11" s="1"/>
       <c r="D11" s="1">
         <v>-22.851897999999998</v>
       </c>
@@ -1922,58 +1766,97 @@
       <c r="F11" s="6">
         <v>46235.40347222222</v>
       </c>
-      <c r="G11" s="1" t="s">
+      <c r="H11" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="H11" s="1"/>
       <c r="I11" s="1"/>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>41</v>
       </c>
-      <c r="B12" s="6"/>
+      <c r="B12" s="6">
+        <v>46235.420138888891</v>
+      </c>
       <c r="C12" s="1"/>
-      <c r="D12" s="1"/>
-      <c r="E12" s="1"/>
-      <c r="F12" s="6"/>
-      <c r="H12" s="1"/>
+      <c r="D12" s="1">
+        <v>-22.478701000000001</v>
+      </c>
+      <c r="E12" s="1">
+        <v>-40.104019000000001</v>
+      </c>
+      <c r="F12" s="6">
+        <v>46234.787499999999</v>
+      </c>
+      <c r="H12" s="1" t="s">
+        <v>69</v>
+      </c>
       <c r="I12" s="1"/>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>14</v>
       </c>
-      <c r="B13" s="6"/>
+      <c r="B13" s="6">
+        <v>46235.420138888891</v>
+      </c>
       <c r="C13" s="1"/>
-      <c r="D13" s="1"/>
-      <c r="E13" s="1"/>
-      <c r="F13" s="6"/>
-      <c r="H13" s="1"/>
+      <c r="D13" s="1">
+        <v>-23.321667000000001</v>
+      </c>
+      <c r="E13" s="1">
+        <v>-42.959999000000003</v>
+      </c>
+      <c r="F13" s="6">
+        <v>46232.784722222219</v>
+      </c>
+      <c r="H13" s="1" t="s">
+        <v>66</v>
+      </c>
       <c r="I13" s="1"/>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>43</v>
       </c>
-      <c r="B14" s="6"/>
+      <c r="B14" s="6">
+        <v>46235.420138888891</v>
+      </c>
       <c r="C14" s="1"/>
-      <c r="D14" s="1"/>
-      <c r="E14" s="1"/>
-      <c r="F14" s="6"/>
-      <c r="H14" s="1"/>
+      <c r="D14" s="1">
+        <v>-23.29213</v>
+      </c>
+      <c r="E14" s="1">
+        <v>-43.021500000000003</v>
+      </c>
+      <c r="F14" s="6">
+        <v>46233.212500000001</v>
+      </c>
+      <c r="H14" s="1" t="s">
+        <v>66</v>
+      </c>
       <c r="I14" s="1"/>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>19</v>
       </c>
-      <c r="B15" s="6"/>
+      <c r="B15" s="6">
+        <v>46235.420138888891</v>
+      </c>
       <c r="C15" s="1"/>
-      <c r="D15" s="1"/>
-      <c r="E15" s="1"/>
-      <c r="F15" s="6"/>
-      <c r="H15" s="1"/>
+      <c r="D15" s="1">
+        <v>-24.742044</v>
+      </c>
+      <c r="E15" s="1">
+        <v>-42.376553000000001</v>
+      </c>
+      <c r="F15" s="6">
+        <v>46232.605555555558</v>
+      </c>
+      <c r="H15" s="1" t="s">
+        <v>69</v>
+      </c>
       <c r="I15" s="1"/>
     </row>
     <row r="18" spans="10:10" x14ac:dyDescent="0.25">
